--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\Nova pasta\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\Github\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47FA2D6-B935-42F7-B143-DD1BB91A85D4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C85AD7-7051-4A56-96BE-381321B2F131}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -653,21 +653,21 @@
         <v>8</v>
       </c>
       <c r="C4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G9" si="0">SUM(C4:F4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="14.5">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\Github\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\desculpa ai\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C85AD7-7051-4A56-96BE-381321B2F131}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2561D49B-74CC-4F12-83ED-64C3BF8CE513}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -600,17 +600,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:K100"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="8" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="8" width="8.7109375" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="11.453125" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" ht="14.5">
+    <row r="2" spans="2:10">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -624,7 +624,7 @@
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:10" ht="14.5">
+    <row r="3" spans="2:10">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,29 +648,29 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:10" ht="14.5">
+    <row r="4" spans="2:10">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G9" si="0">SUM(C4:F4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" ht="14.5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
@@ -692,7 +692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="14.5">
+    <row r="6" spans="2:10">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:10" ht="14.5">
+    <row r="7" spans="2:10">
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -736,7 +736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10" ht="14.5">
+    <row r="8" spans="2:10">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
@@ -758,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="14.5">
+    <row r="9" spans="2:10">
       <c r="B9" s="7" t="s">
         <v>14</v>
       </c>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:10" ht="14.5">
+    <row r="10" spans="2:10">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -790,7 +790,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="13" spans="2:10" ht="14.5">
+    <row r="13" spans="2:10">
       <c r="B13" s="10" t="s">
         <v>15</v>
       </c>
@@ -800,7 +800,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:10" ht="14.5">
+    <row r="14" spans="2:10">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -820,7 +820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="14.5">
+    <row r="15" spans="2:10">
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
@@ -833,7 +833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="14.5">
+    <row r="16" spans="2:10">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
@@ -846,7 +846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.5">
+    <row r="17" spans="1:11">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
@@ -859,7 +859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.5">
+    <row r="18" spans="1:11">
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.5">
+    <row r="19" spans="1:11">
       <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.5">
+    <row r="20" spans="1:11">
       <c r="B20" s="7" t="s">
         <v>14</v>
       </c>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20399"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\desculpa ai\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\cloone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2561D49B-74CC-4F12-83ED-64C3BF8CE513}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC8A1D6C-7E73-449B-824A-F594C4DED87A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="20">
   <si>
     <t>AGOSTO</t>
   </si>
@@ -64,9 +64,6 @@
     <t>Felipe Rodrigues</t>
   </si>
   <si>
-    <t>Victor Gonçalves</t>
-  </si>
-  <si>
     <t>SETEMBRO</t>
   </si>
   <si>
@@ -77,13 +74,19 @@
   </si>
   <si>
     <t>DEZEMBRO</t>
+  </si>
+  <si>
+    <t>Gabriel Andrade</t>
+  </si>
+  <si>
+    <t>,</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -599,18 +602,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:K100"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A2:L100"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="8" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -624,7 +627,7 @@
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,7 +651,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:10">
+    <row r="4" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -670,7 +673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="2:10">
+    <row r="5" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
@@ -692,7 +695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:10">
+    <row r="6" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
@@ -713,8 +716,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:10">
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -736,7 +742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:10">
+    <row r="8" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B8" s="4" t="s">
         <v>13</v>
       </c>
@@ -758,9 +764,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:10">
+    <row r="9" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B9" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" s="7">
         <v>0</v>
@@ -773,14 +779,14 @@
         <v>0</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="2:10">
+    <row r="10" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -790,9 +796,9 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="13" spans="2:10">
+    <row r="13" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B13" s="10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="11"/>
       <c r="D13" s="11"/>
@@ -800,7 +806,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:10">
+    <row r="14" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -820,7 +826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:10">
+    <row r="15" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
@@ -833,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:10">
+    <row r="16" spans="2:12" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
@@ -846,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
@@ -859,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
@@ -872,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
         <v>13</v>
       </c>
@@ -885,9 +891,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B20" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
@@ -898,7 +904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" customHeight="1">
+    <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="9"/>
       <c r="B21" s="8"/>
       <c r="C21" s="8"/>
@@ -911,11 +917,11 @@
       <c r="J21" s="9"/>
       <c r="K21" s="9"/>
     </row>
-    <row r="22" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="23" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="24" spans="1:11" ht="15.75" customHeight="1">
+    <row r="22" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="23" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="24" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C24" s="11"/>
       <c r="D24" s="11"/>
@@ -923,7 +929,7 @@
       <c r="F24" s="11"/>
       <c r="G24" s="12"/>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1">
+    <row r="25" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>2</v>
       </c>
@@ -943,7 +949,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" customHeight="1">
+    <row r="26" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="4" t="s">
         <v>8</v>
       </c>
@@ -956,7 +962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.75" customHeight="1">
+    <row r="27" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4" t="s">
         <v>10</v>
       </c>
@@ -969,7 +975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="15.75" customHeight="1">
+    <row r="28" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="4" t="s">
         <v>11</v>
       </c>
@@ -982,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="15.75" customHeight="1">
+    <row r="29" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="4" t="s">
         <v>12</v>
       </c>
@@ -995,7 +1001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="15.75" customHeight="1">
+    <row r="30" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="4" t="s">
         <v>13</v>
       </c>
@@ -1008,9 +1014,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="15.75" customHeight="1">
+    <row r="31" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
@@ -1021,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15.75" customHeight="1">
+    <row r="32" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="9"/>
       <c r="B32" s="8"/>
       <c r="C32" s="8"/>
@@ -1034,11 +1040,11 @@
       <c r="J32" s="9"/>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="34" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="35" spans="1:11" ht="15.75" customHeight="1">
+    <row r="33" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="11"/>
       <c r="D35" s="11"/>
@@ -1046,7 +1052,7 @@
       <c r="F35" s="11"/>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="1:11" ht="15.75" customHeight="1">
+    <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
         <v>2</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="15.75" customHeight="1">
+    <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
@@ -1079,7 +1085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="15.75" customHeight="1">
+    <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="4" t="s">
         <v>10</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="15.75" customHeight="1">
+    <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="4" t="s">
         <v>11</v>
       </c>
@@ -1105,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="15.75" customHeight="1">
+    <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4" t="s">
         <v>12</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="15.75" customHeight="1">
+    <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="4" t="s">
         <v>13</v>
       </c>
@@ -1131,9 +1137,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="15.75" customHeight="1">
+    <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
@@ -1144,7 +1150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="15.75" customHeight="1">
+    <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9"/>
       <c r="B43" s="8"/>
       <c r="C43" s="8"/>
@@ -1157,11 +1163,11 @@
       <c r="J43" s="9"/>
       <c r="K43" s="9"/>
     </row>
-    <row r="44" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="45" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="46" spans="1:11" ht="15.75" customHeight="1">
+    <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" s="11"/>
       <c r="D46" s="11"/>
@@ -1169,7 +1175,7 @@
       <c r="F46" s="11"/>
       <c r="G46" s="12"/>
     </row>
-    <row r="47" spans="1:11" ht="15.75" customHeight="1">
+    <row r="47" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
@@ -1189,7 +1195,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="15.75" customHeight="1">
+    <row r="48" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="4" t="s">
         <v>8</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="15.75" customHeight="1">
+    <row r="49" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="4" t="s">
         <v>10</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="15.75" customHeight="1">
+    <row r="50" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="4" t="s">
         <v>11</v>
       </c>
@@ -1228,7 +1234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="15.75" customHeight="1">
+    <row r="51" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="4" t="s">
         <v>12</v>
       </c>
@@ -1241,7 +1247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="15.75" customHeight="1">
+    <row r="52" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="4" t="s">
         <v>13</v>
       </c>
@@ -1254,9 +1260,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="15.75" customHeight="1">
+    <row r="53" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="7" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
@@ -1267,7 +1273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="15.75" customHeight="1">
+    <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="9"/>
       <c r="B54" s="8"/>
       <c r="C54" s="8"/>
@@ -1280,52 +1286,52 @@
       <c r="J54" s="9"/>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="56" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="57" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="58" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="59" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="60" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="61" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="62" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="63" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="64" spans="1:11" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="B46:G46"/>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB2EC33D-661D-44F1-9F22-B7CC3103D397}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415AA6D5-26C0-47CA-BB85-8052132C9BF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\Nova pasta\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{415AA6D5-26C0-47CA-BB85-8052132C9BF4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08EEFF7-CB37-4EF7-90D8-7DFB95CB635A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -645,19 +645,21 @@
       <c r="C5" s="4">
         <v>1</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -667,7 +669,9 @@
       <c r="C6" s="4">
         <v>0</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\Nova pasta\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08EEFF7-CB37-4EF7-90D8-7DFB95CB635A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92AB92-0F56-4ABA-9C7E-754E92EB4B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -646,20 +646,20 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:12">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE92AB92-0F56-4ABA-9C7E-754E92EB4B18}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F2D41E-3AD3-4EDE-88B6-E696348C4483}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -624,18 +624,20 @@
       <c r="D4" s="4">
         <v>4</v>
       </c>
-      <c r="E4" s="4"/>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G9" si="0">SUM(C4:F4)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -648,18 +650,20 @@
       <c r="D5" s="4">
         <v>2</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -699,18 +703,20 @@
       <c r="D7" s="4">
         <v>3</v>
       </c>
-      <c r="E7" s="4"/>
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
       <c r="F7" s="4"/>
       <c r="G7" s="4">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -747,18 +753,20 @@
       <c r="D9" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="7"/>
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:12">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\Nova pasta\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F2D41E-3AD3-4EDE-88B6-E696348C4483}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9535E9CB-4CF7-4582-8037-CD900A5B2D01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,19 +651,19 @@
         <v>2</v>
       </c>
       <c r="E5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="2:12">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20399"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\Nova pasta\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\clone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9535E9CB-4CF7-4582-8037-CD900A5B2D01}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140D9B3B-7E82-4E14-8CB8-5FBA7D841C25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="179021"/>
 </workbook>
 </file>
 
@@ -566,17 +566,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:L100"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="8" width="8.7109375" customWidth="1"/>
+    <col min="1" max="1" width="4.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.453125" customWidth="1"/>
+    <col min="3" max="8" width="8.7265625" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
+    <col min="10" max="10" width="11.453125" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
+    <row r="2" spans="2:12" ht="14.5">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:12">
+    <row r="3" spans="2:12" ht="14.5">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -614,7 +614,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:12">
+    <row r="4" spans="2:12" ht="14.5">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -625,22 +625,24 @@
         <v>4</v>
       </c>
       <c r="E4" s="4">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="F4" s="4"/>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G9" si="0">SUM(C4:F4)</f>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="14.5">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
@@ -666,7 +668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:12">
+    <row r="6" spans="2:12" ht="14.5">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
@@ -693,7 +695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12">
+    <row r="7" spans="2:12" ht="14.5">
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
@@ -719,7 +721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:12">
+    <row r="8" spans="2:12" ht="14.5">
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
@@ -743,7 +745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:12">
+    <row r="9" spans="2:12" ht="14.5">
       <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
@@ -769,7 +771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="2:12">
+    <row r="10" spans="2:12" ht="14.5">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -779,7 +781,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" ht="14.5">
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
@@ -789,7 +791,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:12">
+    <row r="14" spans="2:12" ht="14.5">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -809,7 +811,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:12">
+    <row r="15" spans="2:12" ht="14.5">
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
@@ -822,7 +824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:12">
+    <row r="16" spans="2:12" ht="14.5">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
@@ -835,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="14.5">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
@@ -848,7 +850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" ht="14.5">
       <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
@@ -861,7 +863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" ht="14.5">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
@@ -874,7 +876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" ht="14.5">
       <c r="B20" s="7" t="s">
         <v>15</v>
       </c>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20399"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo.DESKTOP-FFTGG6Q\Desktop\clone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{140D9B3B-7E82-4E14-8CB8-5FBA7D841C25}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B54AC8C-90DE-4015-94C5-D66723ECA6D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="179021"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -566,17 +566,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:L100"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="4.81640625" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="8" width="8.7265625" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="8" width="8.7109375" customWidth="1"/>
     <col min="9" max="9" width="15" customWidth="1"/>
-    <col min="10" max="10" width="11.453125" customWidth="1"/>
-    <col min="11" max="11" width="8.7265625" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" customWidth="1"/>
+    <col min="11" max="11" width="8.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="14.5">
+    <row r="2" spans="2:12">
       <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
@@ -590,7 +590,7 @@
       </c>
       <c r="J2" s="14"/>
     </row>
-    <row r="3" spans="2:12" ht="14.5">
+    <row r="3" spans="2:12">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
@@ -614,7 +614,7 @@
       </c>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="2:12" ht="14.5">
+    <row r="4" spans="2:12">
       <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
@@ -628,21 +628,21 @@
         <v>3</v>
       </c>
       <c r="F4" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4">
         <f t="shared" ref="G4:G9" si="0">SUM(C4:F4)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="14.5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
       <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
@@ -668,7 +668,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="2:12" ht="14.5">
+    <row r="6" spans="2:12">
       <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
@@ -695,7 +695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:12" ht="14.5">
+    <row r="7" spans="2:12">
       <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
@@ -721,7 +721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:12" ht="14.5">
+    <row r="8" spans="2:12">
       <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
@@ -745,7 +745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="2:12" ht="14.5">
+    <row r="9" spans="2:12">
       <c r="B9" s="7" t="s">
         <v>15</v>
       </c>
@@ -758,20 +758,22 @@
       <c r="E9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="7">
+        <v>1</v>
+      </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>15</v>
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="14.5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12">
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -781,7 +783,7 @@
       <c r="I10" s="8"/>
       <c r="J10" s="8"/>
     </row>
-    <row r="13" spans="2:12" ht="14.5">
+    <row r="13" spans="2:12">
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
@@ -791,7 +793,7 @@
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
     </row>
-    <row r="14" spans="2:12" ht="14.5">
+    <row r="14" spans="2:12">
       <c r="B14" s="1" t="s">
         <v>2</v>
       </c>
@@ -811,7 +813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="2:12" ht="14.5">
+    <row r="15" spans="2:12">
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
@@ -824,7 +826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:12" ht="14.5">
+    <row r="16" spans="2:12">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
@@ -837,7 +839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="14.5">
+    <row r="17" spans="1:11">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
@@ -850,7 +852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="14.5">
+    <row r="18" spans="1:11">
       <c r="B18" s="4" t="s">
         <v>13</v>
       </c>
@@ -863,7 +865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="14.5">
+    <row r="19" spans="1:11">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
@@ -876,7 +878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="14.5">
+    <row r="20" spans="1:11">
       <c r="B20" s="7" t="s">
         <v>15</v>
       </c>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B54AC8C-90DE-4015-94C5-D66723ECA6D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2A3353-3961-47F0-BCE5-938D01B1B307}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\tcc\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\clone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC2A3353-3961-47F0-BCE5-938D01B1B307}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEA51B2-5CB6-49C7-9293-A43EECD3AF1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -665,7 +665,7 @@
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -742,7 +742,7 @@
       </c>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:12">
@@ -770,7 +770,7 @@
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -817,33 +817,39 @@
       <c r="B15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4">
+        <v>4</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G20" si="2">SUM(C15:F15)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="2:12">
       <c r="B16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="4"/>
+      <c r="C16" s="4">
+        <v>3</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:11">
       <c r="B17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="4"/>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
@@ -869,26 +875,30 @@
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4">
+        <v>4</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:11">
       <c r="B20" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="7"/>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\clone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEA51B2-5CB6-49C7-9293-A43EECD3AF1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11939C5C-742D-490F-9BFE-8D79740B8729}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
+++ b/tcc-documentacao/Planejamento/planilhas/horas-trabalhadas-tcc.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\clone\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alunoinfo\Desktop\clone\tcc-etec\tcc-etec\tcc-documentacao\Planejamento\planilhas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11939C5C-742D-490F-9BFE-8D79740B8729}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BC8EE92-081B-4DE3-BC1C-082AC2C297D6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -639,7 +639,7 @@
       </c>
       <c r="J4" s="5">
         <f t="shared" ref="J4:J9" si="1">SUM(G48,G4,G15,G26,G37)</f>
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:12">
@@ -665,7 +665,7 @@
       </c>
       <c r="J5" s="5">
         <f t="shared" si="1"/>
-        <v>8</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="2:12">
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:12">
@@ -742,7 +742,7 @@
       </c>
       <c r="J8" s="5">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="2:12">
@@ -770,7 +770,7 @@
       </c>
       <c r="J9" s="5">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="2:12">
@@ -820,12 +820,14 @@
       <c r="C15" s="4">
         <v>4</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>4</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4">
         <f t="shared" ref="G15:G20" si="2">SUM(C15:F15)</f>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="2:12">
@@ -835,12 +837,14 @@
       <c r="C16" s="4">
         <v>3</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>10</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -863,12 +867,14 @@
         <v>13</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>4</v>
+      </c>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -878,12 +884,14 @@
       <c r="C19" s="4">
         <v>4</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>2</v>
+      </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -893,12 +901,14 @@
       <c r="C20" s="7">
         <v>1</v>
       </c>
-      <c r="D20" s="7"/>
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="7">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1">
